--- a/scenarios/Coal_Flexibilisation/sub_scenarios/extendable_technologies.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/extendable_technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rlinstitutde-my.sharepoint.com/personal/agatha_majcher_rl-institut_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_DC9B28A12CBD826C6EDA977998B8ADD252B1F987" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC1B6717-45A3-48E4-B17D-5A4AD6479CD6}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_DC9B28A12CBD826C6EDA977998B8ADD252B1F987" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F2D2659-A92A-4C5C-9466-01E42780E8D0}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="-15090" windowWidth="17880" windowHeight="14670" tabRatio="629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="629" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="active" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3598" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3620" uniqueCount="92">
   <si>
     <t>scenario</t>
   </si>
@@ -330,13 +330,20 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -569,7 +576,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -690,243 +697,298 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="12" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="12" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="13" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="13" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="13" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="13" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="13" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="13" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="13" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="14" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="14" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="13" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="13" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="13" borderId="7" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="13" borderId="7" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="15" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="15" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="12" fillId="20" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="20" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="21" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="21" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="13" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="13" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="13" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="13" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="20">
     <cellStyle name="Assumption" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Excel Built-in Bad" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Excel Built-in Bad 2" xfId="17" xr:uid="{D76F19D5-1531-4567-B1C7-2EDC3C76552C}"/>
     <cellStyle name="Excel Built-in Good" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Excel Built-in Good 2" xfId="16" xr:uid="{1C89B2C4-2547-4CB1-A1A3-410C1396264B}"/>
     <cellStyle name="Excel Built-in Input" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Excel Built-in Input 2" xfId="14" xr:uid="{0FFE4B84-F677-4C19-AF94-5F046B417308}"/>
     <cellStyle name="Excel Built-in Neutral" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Excel Built-in Neutral 2" xfId="15" xr:uid="{CB9D40D8-D0B4-4357-8A79-9DAB9CC546F5}"/>
     <cellStyle name="Excel Built-in Output" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Excel Built-in Output 2" xfId="13" xr:uid="{7515744C-8CB6-4F5D-8CD7-325BC3C64649}"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Percent 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Percent 2 2" xfId="12" xr:uid="{6202E98D-74B6-40C7-80E9-9673C854E0DB}"/>
     <cellStyle name="Prozent" xfId="9" builtinId="5"/>
+    <cellStyle name="Prozent 2" xfId="18" xr:uid="{5C20D995-3637-4FA5-85E2-F945FE1F63E4}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Standard 2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Standard 2 3" xfId="19" xr:uid="{CD6C0324-847A-48CC-917E-6302435CABD4}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1568,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" style="1" customWidth="1"/>
@@ -1590,56 +1652,80 @@
     <col min="22" max="22" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="17"/>
-      <c r="J1" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
+    <row r="1" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="75" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="75" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="P1" s="75" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q1" s="75" t="s">
+        <v>76</v>
+      </c>
+      <c r="R1" s="75" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="75" t="s">
+        <v>81</v>
+      </c>
+      <c r="T1" s="75" t="s">
+        <v>78</v>
+      </c>
+      <c r="U1" s="75" t="s">
+        <v>80</v>
+      </c>
+      <c r="V1" s="75" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>33</v>
+      <c r="B2" s="40" t="s">
+        <v>31</v>
       </c>
       <c r="C2" s="48" t="s">
         <v>36</v>
@@ -1656,34 +1742,34 @@
       <c r="G2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="28" t="s">
+      <c r="I2" s="17"/>
+      <c r="J2" s="37" t="s">
         <v>37</v>
       </c>
       <c r="K2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
     </row>
     <row r="3" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="25" t="s">
-        <v>34</v>
+      <c r="B3" s="21" t="s">
+        <v>33</v>
       </c>
       <c r="C3" s="48" t="s">
         <v>36</v>
@@ -1700,46 +1786,46 @@
       <c r="G3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="38"/>
-      <c r="J3" s="26" t="s">
+      <c r="I3" s="10"/>
+      <c r="J3" s="28" t="s">
         <v>37</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
     </row>
     <row r="4" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="53" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="55" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>37</v>
+      <c r="F4" s="49" t="s">
+        <v>38</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>37</v>
@@ -1770,13 +1856,13 @@
       <c r="A5" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>26</v>
+      <c r="B5" s="25" t="s">
+        <v>29</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="26" t="s">
         <v>37</v>
       </c>
       <c r="E5" s="55" t="s">
@@ -1788,59 +1874,39 @@
       <c r="G5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="28" t="s">
+      <c r="H5" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="I5" s="38"/>
+      <c r="J5" s="26" t="s">
         <v>37</v>
       </c>
       <c r="K5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="S5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="T5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="U5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="V5" s="10"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
     </row>
     <row r="6" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="25" t="s">
-        <v>27</v>
+      <c r="B6" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="28" t="s">
         <v>37</v>
       </c>
       <c r="E6" s="55" t="s">
@@ -1852,60 +1918,60 @@
       <c r="G6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="26" t="s">
+      <c r="H6" s="10"/>
+      <c r="I6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="26" t="s">
+      <c r="J6" s="28" t="s">
         <v>37</v>
       </c>
       <c r="K6" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26" t="s">
+      <c r="L6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="26" t="s">
+      <c r="N6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="26" t="s">
+      <c r="O6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="P6" s="26" t="s">
+      <c r="P6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="26" t="s">
+      <c r="Q6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="R6" s="26" t="s">
+      <c r="R6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="S6" s="26" t="s">
+      <c r="S6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="T6" s="26" t="s">
+      <c r="T6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="U6" s="26" t="s">
+      <c r="U6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="V6" s="38"/>
+      <c r="V6" s="10"/>
     </row>
     <row r="7" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>23</v>
+      <c r="B7" s="25" t="s">
+        <v>27</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="55" t="s">
-        <v>35</v>
+      <c r="D7" s="26" t="s">
+        <v>37</v>
       </c>
       <c r="E7" s="55" t="s">
         <v>40</v>
@@ -1916,38 +1982,54 @@
       <c r="G7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="28" t="s">
+      <c r="H7" s="38"/>
+      <c r="I7" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="26" t="s">
         <v>37</v>
       </c>
       <c r="K7" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="28" t="s">
+      <c r="L7" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="28" t="s">
+      <c r="M7" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
+      <c r="N7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="S7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="T7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="U7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="V7" s="38"/>
     </row>
     <row r="8" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="53" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>37</v>
@@ -1988,14 +2070,14 @@
       <c r="S8" s="10"/>
       <c r="T8" s="10"/>
       <c r="U8" s="10"/>
-      <c r="V8" s="38"/>
+      <c r="V8" s="10"/>
     </row>
     <row r="9" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>18</v>
+      <c r="B9" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>37</v>
@@ -2012,38 +2094,38 @@
       <c r="G9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="26" t="s">
+      <c r="H9" s="10"/>
+      <c r="I9" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="26" t="s">
+      <c r="J9" s="28" t="s">
         <v>37</v>
       </c>
       <c r="K9" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="26" t="s">
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="26" t="s">
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
       <c r="V9" s="38"/>
     </row>
     <row r="10" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>19</v>
+      <c r="B10" s="25" t="s">
+        <v>18</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>37</v>
@@ -2060,38 +2142,38 @@
       <c r="G10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="28" t="s">
+      <c r="H10" s="38"/>
+      <c r="I10" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="26" t="s">
         <v>37</v>
       </c>
       <c r="K10" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="28" t="s">
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="28" t="s">
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
       <c r="V10" s="38"/>
     </row>
     <row r="11" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>20</v>
+      <c r="B11" s="21" t="s">
+        <v>19</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>37</v>
@@ -2108,38 +2190,38 @@
       <c r="G11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="26" t="s">
+      <c r="H11" s="10"/>
+      <c r="I11" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="26" t="s">
+      <c r="J11" s="28" t="s">
         <v>37</v>
       </c>
       <c r="K11" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="26" t="s">
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="26" t="s">
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
       <c r="V11" s="38"/>
     </row>
     <row r="12" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>21</v>
+      <c r="B12" s="25" t="s">
+        <v>20</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>37</v>
@@ -2156,38 +2238,38 @@
       <c r="G12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="28" t="s">
+      <c r="H12" s="38"/>
+      <c r="I12" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="26" t="s">
         <v>37</v>
       </c>
       <c r="K12" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="28" t="s">
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="28" t="s">
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
       <c r="V12" s="38"/>
     </row>
     <row r="13" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>22</v>
+      <c r="B13" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>37</v>
@@ -2204,38 +2286,38 @@
       <c r="G13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="38"/>
-      <c r="I13" s="26" t="s">
+      <c r="H13" s="10"/>
+      <c r="I13" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="26" t="s">
+      <c r="J13" s="28" t="s">
         <v>37</v>
       </c>
       <c r="K13" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="26" t="s">
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="26" t="s">
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
       <c r="V13" s="38"/>
     </row>
     <row r="14" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>15</v>
+      <c r="B14" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>37</v>
@@ -2252,46 +2334,30 @@
       <c r="G14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="28" t="s">
+      <c r="H14" s="38"/>
+      <c r="I14" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="28" t="s">
+      <c r="J14" s="26" t="s">
         <v>37</v>
       </c>
       <c r="K14" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L14" s="28" t="s">
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="M14" s="28" t="s">
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="O14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="P14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="R14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="S14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="T14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="U14" s="28" t="s">
-        <v>37</v>
-      </c>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
       <c r="V14" s="38"/>
     </row>
     <row r="15" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2299,7 +2365,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>37</v>
@@ -2317,29 +2383,53 @@
         <v>37</v>
       </c>
       <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
+      <c r="I15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>37</v>
+      </c>
       <c r="K15" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
+      <c r="L15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="P15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="R15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="S15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="T15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="U15" s="28" t="s">
+        <v>37</v>
+      </c>
       <c r="V15" s="38"/>
     </row>
     <row r="16" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="25" t="s">
-        <v>11</v>
+      <c r="B16" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>37</v>
@@ -2356,30 +2446,30 @@
       <c r="G16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
       <c r="K16" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
       <c r="V16" s="38"/>
     </row>
     <row r="17" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>8</v>
+      <c r="B17" s="25" t="s">
+        <v>11</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>37</v>
@@ -2396,36 +2486,36 @@
       <c r="G17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
       <c r="K17" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
       <c r="V17" s="38"/>
     </row>
     <row r="18" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>12</v>
+      <c r="B18" s="21" t="s">
+        <v>8</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>37</v>
+      <c r="D18" s="55" t="s">
+        <v>35</v>
       </c>
       <c r="E18" s="55" t="s">
         <v>40</v>
@@ -2436,36 +2526,36 @@
       <c r="G18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
       <c r="K18" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="38"/>
-      <c r="S18" s="38"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="38"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
       <c r="V18" s="38"/>
     </row>
     <row r="19" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>13</v>
+      <c r="B19" s="25" t="s">
+        <v>12</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="55" t="s">
-        <v>35</v>
+      <c r="D19" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E19" s="55" t="s">
         <v>40</v>
@@ -2476,32 +2566,32 @@
       <c r="G19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
       <c r="K19" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
       <c r="V19" s="38"/>
     </row>
     <row r="20" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="45" t="s">
+      <c r="B20" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D20" s="55" t="s">
@@ -2510,29 +2600,69 @@
       <c r="E20" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="45" t="s">
+      <c r="G20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="39"/>
-      <c r="T20" s="39"/>
-      <c r="U20" s="39"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
       <c r="V20" s="38"/>
+    </row>
+    <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="39"/>
+      <c r="U21" s="39"/>
+      <c r="V21" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/scenarios/Coal_Flexibilisation/sub_scenarios/extendable_technologies.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/extendable_technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rlinstitutde-my.sharepoint.com/personal/agatha_majcher_rl-institut_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_DC9B28A12CBD826C6EDA977998B8ADD252B1F987" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F2D2659-A92A-4C5C-9466-01E42780E8D0}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_DC9B28A12CBD826C6EDA977998B8ADD252B1F987" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FEADEF6-64FB-4706-BC92-B6FE8B3FE694}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="629" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10515" yWindow="-15840" windowWidth="17880" windowHeight="15465" tabRatio="629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="active" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3620" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3620" uniqueCount="93">
   <si>
     <t>scenario</t>
   </si>
@@ -321,6 +321,9 @@
   <si>
     <t>true</t>
   </si>
+  <si>
+    <t>false</t>
+  </si>
 </sst>
 </file>
 
@@ -442,7 +445,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -572,6 +575,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFF8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
@@ -746,7 +755,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -967,6 +976,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="13" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Assumption" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1090,6 +1102,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1498,8 +1514,8 @@
       <c r="C16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="74" t="s">
-        <v>91</v>
+      <c r="D16" s="80" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1512,8 +1528,8 @@
       <c r="C17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="74" t="s">
-        <v>91</v>
+      <c r="D17" s="80" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1582,8 +1598,8 @@
       <c r="C22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="74" t="s">
-        <v>91</v>
+      <c r="D22" s="80" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
